--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487880_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487880_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.887</v>
+        <v>6.9267</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0079</v>
+        <v>5.9008</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8791</v>
+        <v>1.0259</v>
       </c>
       <c r="G2" t="n">
         <v>5.0712</v>
@@ -610,13 +610,13 @@
         <v>2.4974</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1103</v>
+        <v>0.1499</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2668</v>
+        <v>0.1596</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1565</v>
+        <v>-0.0097</v>
       </c>
       <c r="V2" t="n">
         <v>-0.5838</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9535</v>
+        <v>5.01</v>
       </c>
       <c r="E3" t="n">
-        <v>7.199</v>
+        <v>7.0499</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.2454</v>
+        <v>-2.0399</v>
       </c>
       <c r="G3" t="n">
         <v>4.034</v>
@@ -688,13 +688,13 @@
         <v>1.4568</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0992</v>
+        <v>-0.0427</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0562</v>
+        <v>-0.2052</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.043</v>
+        <v>0.1625</v>
       </c>
       <c r="V3" t="n">
         <v>-0.23</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. KOCIC</t>
+          <t>L. GARCIA MUÑOZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8941</v>
+        <v>2.5488</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6932</v>
+        <v>4.2347</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2009</v>
+        <v>-1.6859</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2714</v>
+        <v>0.1406</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.7868</v>
+        <v>-1.2236</v>
       </c>
       <c r="I4" t="n">
-        <v>2.0582</v>
+        <v>1.3642</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3083</v>
+        <v>0.888</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.8191000000000001</v>
+        <v>0.279</v>
       </c>
       <c r="L4" t="n">
-        <v>1.1275</v>
+        <v>0.609</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.037</v>
+        <v>-0.7474</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9677</v>
+        <v>-1.5026</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9307</v>
+        <v>0.7552</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6649</v>
+        <v>1.2487</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6649</v>
+        <v>2.2893</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9578</v>
+        <v>-1.1756</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3849</v>
+        <v>-0.5129</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5729</v>
+        <v>-0.6627999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>2.3351</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>4.9001</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-2.565</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. SERRANO ALVAREZ</t>
+          <t>S. KOCIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4452</v>
+        <v>2.1872</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6888</v>
+        <v>0.5441</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7564</v>
+        <v>1.643</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.4469</v>
+        <v>0.2714</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7252999999999999</v>
+        <v>-1.7868</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2784</v>
+        <v>2.0582</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0434</v>
+        <v>0.3083</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7691</v>
+        <v>-0.8191000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2743</v>
+        <v>1.1275</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4902</v>
+        <v>-0.037</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4943</v>
+        <v>-0.9677</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0041</v>
+        <v>0.9307</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.4162</v>
+        <v>1.6649</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>1.6649</v>
       </c>
       <c r="S5" t="n">
-        <v>1.327</v>
+        <v>0.2509</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5153</v>
+        <v>0.2358</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8117</v>
+        <v>0.0151</v>
       </c>
       <c r="V5" t="n">
-        <v>1.9813</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.2112</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. TEIXEIRA DO VALE DIAS</t>
+          <t>M. SERRANO ALVAREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7371</v>
+        <v>1.7332</v>
       </c>
       <c r="E6" t="n">
-        <v>0.717</v>
+        <v>1.153</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0201</v>
+        <v>0.5802</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3411</v>
+        <v>-0.4469</v>
       </c>
       <c r="H6" t="n">
-        <v>2.0555</v>
+        <v>-0.7252999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7144</v>
+        <v>0.2784</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3941</v>
+        <v>1.0434</v>
       </c>
       <c r="K6" t="n">
-        <v>1.8229</v>
+        <v>0.7691</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.4287</v>
+        <v>0.2743</v>
       </c>
       <c r="M6" t="n">
-        <v>0.947</v>
+        <v>-1.4902</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2326</v>
+        <v>-1.4943</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7144</v>
+        <v>0.0041</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6244</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2081</v>
+        <v>-2.0812</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8325</v>
+        <v>1.6649</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2284</v>
+        <v>0.6151</v>
       </c>
       <c r="T6" t="n">
-        <v>0.531</v>
+        <v>-0.0204</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7594</v>
+        <v>0.6355</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.9813</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.2112</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. GARCIA MUÑOZ</t>
+          <t>T. TEIXEIRA DO VALE DIAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2674</v>
+        <v>1.6696</v>
       </c>
       <c r="E7" t="n">
-        <v>3.2469</v>
+        <v>0.5027</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.9795</v>
+        <v>1.1669</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1406</v>
+        <v>1.3411</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.2236</v>
+        <v>2.0555</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3642</v>
+        <v>-0.7144</v>
       </c>
       <c r="J7" t="n">
-        <v>0.888</v>
+        <v>0.3941</v>
       </c>
       <c r="K7" t="n">
-        <v>0.279</v>
+        <v>1.8229</v>
       </c>
       <c r="L7" t="n">
-        <v>0.609</v>
+        <v>-1.4287</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7474</v>
+        <v>0.947</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.5026</v>
+        <v>0.2326</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7552</v>
+        <v>0.7144</v>
       </c>
       <c r="P7" t="n">
-        <v>1.2487</v>
+        <v>0.6244</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0406</v>
+        <v>-0.2081</v>
       </c>
       <c r="R7" t="n">
-        <v>2.2893</v>
+        <v>0.8325</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.4569</v>
+        <v>-0.2959</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.5006</v>
+        <v>0.3167</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9564</v>
+        <v>-0.6126</v>
       </c>
       <c r="V7" t="n">
-        <v>2.3351</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>4.9001</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.565</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.3408</v>
+        <v>-2.2588</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.5981</v>
+        <v>-2.5748</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2573</v>
+        <v>0.316</v>
       </c>
       <c r="G8" t="n">
         <v>-2.4482</v>
@@ -1078,13 +1078,13 @@
         <v>1.2487</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9114</v>
+        <v>-0.8294</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1338</v>
+        <v>-0.1105</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7776</v>
+        <v>-0.7189</v>
       </c>
       <c r="V8" t="n">
         <v>-0.23</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6848</v>
+        <v>-3.2854</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.9352</v>
+        <v>-3.4477</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2504</v>
+        <v>0.1623</v>
       </c>
       <c r="G9" t="n">
         <v>-0.4363</v>
@@ -1156,13 +1156,13 @@
         <v>0.8325</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0189</v>
+        <v>-0.5816</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8539</v>
+        <v>0.3415</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.835</v>
+        <v>-0.9231</v>
       </c>
       <c r="V9" t="n">
         <v>0.23</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.431</v>
+        <v>-4.9577</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.4947</v>
+        <v>-5.7865</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0637</v>
+        <v>0.8288</v>
       </c>
       <c r="G10" t="n">
         <v>-6.135</v>
@@ -1234,13 +1234,13 @@
         <v>2.0812</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1285</v>
+        <v>0.3448</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2272</v>
+        <v>-0.5191</v>
       </c>
       <c r="U10" t="n">
-        <v>1.0987</v>
+        <v>0.8639</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.5627</v>
+        <v>-5.7562</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.465</v>
+        <v>-4.864</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0977</v>
+        <v>-0.8922</v>
       </c>
       <c r="G11" t="n">
         <v>-2.0252</v>
@@ -1312,13 +1312,13 @@
         <v>1.0406</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.0994</v>
+        <v>-1.2929</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5219</v>
+        <v>0.0791</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.5775</v>
+        <v>-1.372</v>
       </c>
       <c r="V11" t="n">
         <v>-1.3975</v>
@@ -1345,31 +1345,31 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.164999999999998</v>
+        <v>3.817399999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>2.059800000000001</v>
+        <v>2.7122</v>
       </c>
       <c r="F12" t="n">
-        <v>1.1053</v>
+        <v>1.1051</v>
       </c>
       <c r="G12" t="n">
         <v>-0.6332999999999993</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.1233</v>
+        <v>-3.123299999999999</v>
       </c>
       <c r="I12" t="n">
         <v>2.49</v>
       </c>
       <c r="J12" t="n">
-        <v>4.614700000000003</v>
+        <v>4.614700000000001</v>
       </c>
       <c r="K12" t="n">
         <v>5.3701</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.7553000000000001</v>
+        <v>-0.755300000000001</v>
       </c>
       <c r="M12" t="n">
         <v>-5.2478</v>
@@ -1378,7 +1378,7 @@
         <v>-8.4932</v>
       </c>
       <c r="O12" t="n">
-        <v>3.2454</v>
+        <v>3.245400000000001</v>
       </c>
       <c r="P12" t="n">
         <v>5.202999999999999</v>
@@ -1390,13 +1390,13 @@
         <v>15.6088</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.509800000000001</v>
+        <v>-2.8574</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8878</v>
+        <v>-0.2353999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.622100000000001</v>
+        <v>-2.6221</v>
       </c>
       <c r="V12" t="n">
         <v>2.1051</v>
@@ -1405,13 +1405,13 @@
         <v>8.738800000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.6338</v>
+        <v>-6.633800000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. LATORRE SANCHEZ</t>
+          <t>M. JANKOVIC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.6441</v>
+        <v>2.0639</v>
       </c>
       <c r="E13" t="n">
-        <v>3.649</v>
+        <v>1.9398</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0049</v>
+        <v>0.1241</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.8768</v>
+        <v>0.6556</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.9619</v>
+        <v>-0.4735</v>
       </c>
       <c r="I13" t="n">
-        <v>1.085</v>
+        <v>1.1291</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.5377</v>
+        <v>1.1171</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6553</v>
+        <v>0.4901</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1176</v>
+        <v>0.627</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.3391</v>
+        <v>-0.4614</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.3066</v>
+        <v>-0.9636</v>
       </c>
       <c r="O13" t="n">
-        <v>0.9675</v>
+        <v>0.5021</v>
       </c>
       <c r="P13" t="n">
-        <v>1.4568</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.2081</v>
+        <v>-1.0406</v>
       </c>
       <c r="R13" t="n">
-        <v>1.6649</v>
+        <v>0.6244</v>
       </c>
       <c r="S13" t="n">
-        <v>4.3991</v>
+        <v>0.657</v>
       </c>
       <c r="T13" t="n">
-        <v>4.1648</v>
+        <v>0.4658</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2343</v>
+        <v>0.1912</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.3351</v>
+        <v>1.1675</v>
       </c>
       <c r="W13" t="n">
-        <v>0.23</v>
+        <v>1.3975</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.565</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. JANKOVIC</t>
+          <t>W. CABRAL BUERIBERI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.9797</v>
+        <v>0.9599</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9398</v>
+        <v>0.165</v>
       </c>
       <c r="F14" t="n">
-        <v>0.04</v>
+        <v>0.7949000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6556</v>
+        <v>-1.3545</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4735</v>
+        <v>-0.8614000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1291</v>
+        <v>-0.4931</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1171</v>
+        <v>-1.2197</v>
       </c>
       <c r="K14" t="n">
-        <v>0.4901</v>
+        <v>-1.045</v>
       </c>
       <c r="L14" t="n">
-        <v>0.627</v>
+        <v>-0.1747</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4614</v>
+        <v>-0.1348</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.9636</v>
+        <v>0.1836</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5021</v>
+        <v>-0.3184</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.4162</v>
+        <v>0.6244</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0406</v>
+        <v>-0.2081</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6244</v>
+        <v>0.8325</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5728</v>
+        <v>0.5226</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4658</v>
+        <v>0.4253</v>
       </c>
       <c r="U14" t="n">
-        <v>0.107</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>1.1675</v>
       </c>
       <c r="W14" t="n">
-        <v>1.3975</v>
+        <v>1.1675</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.345</v>
+        <v>0.7887</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7524</v>
+        <v>1.4309</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4073</v>
+        <v>-0.6422</v>
       </c>
       <c r="G15" t="n">
         <v>1.38</v>
@@ -1624,13 +1624,13 @@
         <v>0.4162</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7164</v>
+        <v>0.16</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.39</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7849</v>
+        <v>0.55</v>
       </c>
       <c r="V15" t="n">
         <v>-1.1675</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>W. CABRAL BUERIBERI</t>
+          <t>L. SOUMBEY-ALLEY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5607</v>
+        <v>0.5073</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2636</v>
+        <v>2.0725</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8243</v>
+        <v>-1.5652</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.3545</v>
+        <v>4.6427</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8614000000000001</v>
+        <v>3.6009</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4931</v>
+        <v>1.0418</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.2197</v>
+        <v>4.153</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.045</v>
+        <v>4.3277</v>
       </c>
       <c r="L16" t="n">
         <v>-0.1747</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1348</v>
+        <v>0.4897</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1836</v>
+        <v>-0.7268</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3184</v>
+        <v>1.2165</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6244</v>
+        <v>-2.7055</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2081</v>
+        <v>-4.1624</v>
       </c>
       <c r="R16" t="n">
-        <v>0.8325</v>
+        <v>1.4568</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1233</v>
+        <v>0.3215</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0033</v>
+        <v>0.3306</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1266</v>
+        <v>-0.0091</v>
       </c>
       <c r="V16" t="n">
-        <v>1.1675</v>
+        <v>-1.7513</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1675</v>
+        <v>1.7513</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-3.5026</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. SOUMBEY-ALLEY</t>
+          <t>A. LATORRE SANCHEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0745</v>
+        <v>0.1653</v>
       </c>
       <c r="E17" t="n">
-        <v>1.751</v>
+        <v>1.2916</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.8255</v>
+        <v>-1.1263</v>
       </c>
       <c r="G17" t="n">
-        <v>4.6427</v>
+        <v>-0.8768</v>
       </c>
       <c r="H17" t="n">
-        <v>3.6009</v>
+        <v>-1.9619</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0418</v>
+        <v>1.085</v>
       </c>
       <c r="J17" t="n">
-        <v>4.153</v>
+        <v>-0.5377</v>
       </c>
       <c r="K17" t="n">
-        <v>4.3277</v>
+        <v>-0.6553</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.1747</v>
+        <v>0.1176</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4897</v>
+        <v>-0.3391</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7268</v>
+        <v>-1.3066</v>
       </c>
       <c r="O17" t="n">
-        <v>1.2165</v>
+        <v>0.9675</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.7055</v>
+        <v>1.4568</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.1624</v>
+        <v>-0.2081</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4568</v>
+        <v>1.6649</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2603</v>
+        <v>1.9203</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0091</v>
+        <v>1.8074</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2694</v>
+        <v>0.1129</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.7513</v>
+        <v>-2.3351</v>
       </c>
       <c r="W17" t="n">
-        <v>1.7513</v>
+        <v>0.23</v>
       </c>
       <c r="X17" t="n">
-        <v>-3.5026</v>
+        <v>-2.565</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9125</v>
+        <v>0.09</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.433</v>
+        <v>0.7457</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4795</v>
+        <v>-0.6556</v>
       </c>
       <c r="G18" t="n">
         <v>0.5649</v>
@@ -1858,13 +1858,13 @@
         <v>1.6649</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7261</v>
+        <v>0.2765</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.3701</v>
+        <v>-0.1914</v>
       </c>
       <c r="U18" t="n">
-        <v>0.644</v>
+        <v>0.4678</v>
       </c>
       <c r="V18" t="n">
         <v>-1.1675</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9249000000000001</v>
+        <v>-0.9876</v>
       </c>
       <c r="E19" t="n">
         <v>-1.4279</v>
       </c>
       <c r="F19" t="n">
-        <v>0.503</v>
+        <v>0.4404</v>
       </c>
       <c r="G19" t="n">
         <v>-1.3156</v>
@@ -1936,13 +1936,13 @@
         <v>1.2487</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2668</v>
+        <v>0.2042</v>
       </c>
       <c r="T19" t="n">
         <v>0.4625</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1957</v>
+        <v>-0.2583</v>
       </c>
       <c r="V19" t="n">
         <v>0.1238</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>N. DEDOVIC</t>
+          <t>S. CECILIA PEREZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.256</v>
+        <v>-1.4957</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.092</v>
+        <v>-2.2496</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.164</v>
+        <v>0.7539</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.1583</v>
+        <v>-0.5613</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1603</v>
+        <v>0.9597</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.3185</v>
+        <v>-1.521</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0421</v>
+        <v>-0.5081</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9402</v>
+        <v>1.017</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.8981</v>
+        <v>-1.5251</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2004</v>
+        <v>-0.0532</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.78</v>
+        <v>-0.0573</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4204</v>
+        <v>0.0041</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.6244</v>
+        <v>-2.4974</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.0812</v>
+        <v>-3.1218</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4568</v>
+        <v>0.6244</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7033</v>
+        <v>-0.0644</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5129</v>
+        <v>-0.2471</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1904</v>
+        <v>0.1827</v>
       </c>
       <c r="V20" t="n">
-        <v>0.23</v>
+        <v>1.6275</v>
       </c>
       <c r="W20" t="n">
-        <v>0.4599</v>
+        <v>1.6275</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. CECILIA PEREZ</t>
+          <t>N. DEDOVIC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2957</v>
+        <v>-1.6536</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.7854</v>
+        <v>-1.9848</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4896</v>
+        <v>0.3312</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5613</v>
+        <v>-1.1583</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9597</v>
+        <v>0.1603</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.521</v>
+        <v>-1.3185</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5081</v>
+        <v>0.0421</v>
       </c>
       <c r="K21" t="n">
-        <v>1.017</v>
+        <v>0.9402</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.5251</v>
+        <v>-0.8981</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0532</v>
+        <v>-1.2004</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0573</v>
+        <v>-0.78</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0041</v>
+        <v>-0.4204</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.4974</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.1218</v>
+        <v>-2.0812</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6244</v>
+        <v>1.4568</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8643999999999999</v>
+        <v>-0.101</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7829</v>
+        <v>-0.4057</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0815</v>
+        <v>0.3047</v>
       </c>
       <c r="V21" t="n">
-        <v>1.6275</v>
+        <v>0.23</v>
       </c>
       <c r="W21" t="n">
-        <v>1.6275</v>
+        <v>0.4599</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2308</v>
+        <v>-2.8888</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.1953</v>
+        <v>-3.0882</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0355</v>
+        <v>0.1994</v>
       </c>
       <c r="G22" t="n">
         <v>-1.3434</v>
@@ -2170,13 +2170,13 @@
         <v>0.4162</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0144</v>
+        <v>0.3277</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2577</v>
+        <v>0.3648</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.272</v>
+        <v>-0.0372</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,19 +2203,19 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.164899999999999</v>
+        <v>-2.450600000000001</v>
       </c>
       <c r="E23" t="n">
         <v>-1.105</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.0598</v>
+        <v>-1.3454</v>
       </c>
       <c r="G23" t="n">
-        <v>0.6332999999999984</v>
+        <v>0.6332999999999993</v>
       </c>
       <c r="H23" t="n">
-        <v>3.123200000000001</v>
+        <v>3.1232</v>
       </c>
       <c r="I23" t="n">
         <v>-2.4901</v>
@@ -2224,7 +2224,7 @@
         <v>5.247999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>8.4933</v>
+        <v>8.493300000000001</v>
       </c>
       <c r="L23" t="n">
         <v>-3.2453</v>
@@ -2236,7 +2236,7 @@
         <v>-5.3702</v>
       </c>
       <c r="O23" t="n">
-        <v>0.7554000000000001</v>
+        <v>0.7553999999999998</v>
       </c>
       <c r="P23" t="n">
         <v>-5.202999999999999</v>
@@ -2248,22 +2248,22 @@
         <v>10.4058</v>
       </c>
       <c r="S23" t="n">
-        <v>3.509899999999999</v>
+        <v>4.2244</v>
       </c>
       <c r="T23" t="n">
-        <v>2.622199999999999</v>
+        <v>2.6222</v>
       </c>
       <c r="U23" t="n">
-        <v>0.8877999999999999</v>
+        <v>1.6019</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.1051</v>
+        <v>-2.105100000000001</v>
       </c>
       <c r="W23" t="n">
-        <v>6.633699999999999</v>
+        <v>6.6337</v>
       </c>
       <c r="X23" t="n">
-        <v>-8.738799999999999</v>
+        <v>-8.738800000000001</v>
       </c>
     </row>
   </sheetData>
